--- a/invitados.xlsx
+++ b/invitados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brian.fernandez\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36709065-CA30-46EE-9822-3C1FD36FF880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDBFA432-B4CE-492B-9494-BF5C3C4C8570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D3C44EFB-CC1C-46B2-8964-FA404AFB8647}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>codigo</t>
   </si>
@@ -129,6 +129,18 @@
   </si>
   <si>
     <t>Hector &amp; Ana</t>
+  </si>
+  <si>
+    <t>Jairo &amp; Maribel</t>
+  </si>
+  <si>
+    <t>Luz Marina &amp; Reinaldo</t>
+  </si>
+  <si>
+    <t>Omiris</t>
+  </si>
+  <si>
+    <t>Nevis</t>
   </si>
 </sst>
 </file>
@@ -158,15 +170,27 @@
       <scheme val="major"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -184,17 +208,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="4"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -204,31 +217,36 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+  </cellStyleXfs>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="2">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Confirmado" xfId="1" xr:uid="{4ACB1AA5-A5CD-4AFB-B731-5A085A10906A}"/>
+    <cellStyle name="Enviada" xfId="2" xr:uid="{BD681C0D-4532-4C7E-98B7-55EABFEB3FBB}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -561,7 +579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4355357-D613-4929-9CAB-FC2F66DF68B3}">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26.7109375" bestFit="1" customWidth="1"/>
@@ -582,10 +600,10 @@
       <c r="A2">
         <v>101</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="1">
         <v>3</v>
       </c>
     </row>
@@ -593,10 +611,10 @@
       <c r="A3">
         <v>102</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="1">
         <v>4</v>
       </c>
     </row>
@@ -604,10 +622,10 @@
       <c r="A4">
         <v>103</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="1">
         <v>1</v>
       </c>
     </row>
@@ -615,10 +633,10 @@
       <c r="A5">
         <v>104</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="1">
         <v>2</v>
       </c>
     </row>
@@ -626,10 +644,10 @@
       <c r="A6">
         <v>105</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="1">
         <v>1</v>
       </c>
     </row>
@@ -637,10 +655,10 @@
       <c r="A7">
         <v>106</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="1">
         <v>1</v>
       </c>
     </row>
@@ -648,10 +666,10 @@
       <c r="A8">
         <v>107</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="1">
         <v>2</v>
       </c>
     </row>
@@ -659,10 +677,10 @@
       <c r="A9">
         <v>108</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="1">
         <v>1</v>
       </c>
     </row>
@@ -670,10 +688,10 @@
       <c r="A10">
         <v>109</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="1">
         <v>3</v>
       </c>
     </row>
@@ -681,10 +699,10 @@
       <c r="A11">
         <v>110</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="1">
         <v>2</v>
       </c>
     </row>
@@ -692,10 +710,10 @@
       <c r="A12">
         <v>111</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="1">
         <v>2</v>
       </c>
     </row>
@@ -703,10 +721,10 @@
       <c r="A13">
         <v>112</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="1">
         <v>2</v>
       </c>
     </row>
@@ -714,10 +732,10 @@
       <c r="A14">
         <v>113</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="1">
         <v>2</v>
       </c>
     </row>
@@ -725,10 +743,10 @@
       <c r="A15">
         <v>114</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="1">
         <v>2</v>
       </c>
     </row>
@@ -736,10 +754,10 @@
       <c r="A16">
         <v>115</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="1">
         <v>2</v>
       </c>
     </row>
@@ -747,10 +765,10 @@
       <c r="A17">
         <v>116</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="1">
         <v>2</v>
       </c>
     </row>
@@ -758,10 +776,10 @@
       <c r="A18">
         <v>117</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="1">
         <v>2</v>
       </c>
     </row>
@@ -769,10 +787,10 @@
       <c r="A19">
         <v>118</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="2">
         <v>2</v>
       </c>
     </row>
@@ -783,7 +801,7 @@
       <c r="B20" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="3">
         <v>1</v>
       </c>
     </row>
@@ -791,10 +809,10 @@
       <c r="A21">
         <v>120</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="3">
         <v>1</v>
       </c>
     </row>
@@ -802,10 +820,10 @@
       <c r="A22">
         <v>121</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="3">
         <v>3</v>
       </c>
     </row>
@@ -813,10 +831,10 @@
       <c r="A23">
         <v>122</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="3">
         <v>1</v>
       </c>
     </row>
@@ -824,10 +842,10 @@
       <c r="A24">
         <v>123</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="3">
         <v>2</v>
       </c>
     </row>
@@ -838,7 +856,7 @@
       <c r="B25" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="3">
         <v>2</v>
       </c>
     </row>
@@ -846,10 +864,10 @@
       <c r="A26">
         <v>125</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="3">
         <v>2</v>
       </c>
     </row>
@@ -857,10 +875,10 @@
       <c r="A27">
         <v>126</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="3">
         <v>1</v>
       </c>
     </row>
@@ -868,14 +886,59 @@
       <c r="A28">
         <v>127</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="6">
-        <v>2</v>
+      <c r="C28" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>128</v>
+      </c>
+      <c r="B29" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>129</v>
+      </c>
+      <c r="B30" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>130</v>
+      </c>
+      <c r="B31" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>131</v>
+      </c>
+      <c r="B32" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/invitados.xlsx
+++ b/invitados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brian.fernandez\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDBFA432-B4CE-492B-9494-BF5C3C4C8570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B4B797D-8BD2-4457-9B3B-9157D6A4135C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D3C44EFB-CC1C-46B2-8964-FA404AFB8647}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>codigo</t>
   </si>
@@ -141,6 +141,9 @@
   </si>
   <si>
     <t>Nevis</t>
+  </si>
+  <si>
+    <t>Alexa</t>
   </si>
 </sst>
 </file>
@@ -579,7 +582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4355357-D613-4929-9CAB-FC2F66DF68B3}">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26.7109375" bestFit="1" customWidth="1"/>
@@ -937,6 +940,17 @@
         <v>1</v>
       </c>
     </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>132</v>
+      </c>
+      <c r="B33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" s="3">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/invitados.xlsx
+++ b/invitados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\green\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D7A7B0-CC26-4F85-BD02-6B26CA69D564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0877BC21-0FF8-46BF-95B4-5CA23C76CBA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D3C44EFB-CC1C-46B2-8964-FA404AFB8647}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>codigo</t>
   </si>
@@ -156,6 +156,9 @@
   </si>
   <si>
     <t>Carolina</t>
+  </si>
+  <si>
+    <t>Daniel Muñoz</t>
   </si>
 </sst>
 </file>
@@ -594,7 +597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4355357-D613-4929-9CAB-FC2F66DF68B3}">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26.7109375" bestFit="1" customWidth="1"/>
@@ -1007,6 +1010,17 @@
         <v>1</v>
       </c>
     </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>137</v>
+      </c>
+      <c r="B38" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="1">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
